--- a/full/sliding_window_results_window_9.xlsx
+++ b/full/sliding_window_results_window_9.xlsx
@@ -463,13 +463,13 @@
         <v>29.81</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>29.92086429301134</v>
       </c>
       <c r="D2" t="n">
-        <v>-29.81</v>
+        <v>0.1108642930113426</v>
       </c>
       <c r="E2" t="n">
-        <v>888.6360999999999</v>
+        <v>0.01229089146490483</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.92</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>29.75576833558574</v>
       </c>
       <c r="D3" t="n">
-        <v>-29.92</v>
+        <v>-0.1642316644142596</v>
       </c>
       <c r="E3" t="n">
-        <v>895.2064000000001</v>
+        <v>0.02697203959627799</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.98</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>30.13415867165269</v>
       </c>
       <c r="D4" t="n">
-        <v>-29.98</v>
+        <v>0.1541586716526879</v>
       </c>
       <c r="E4" t="n">
-        <v>898.8004000000001</v>
+        <v>0.02376489604572125</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>30.04</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>30.30169986370785</v>
       </c>
       <c r="D5" t="n">
-        <v>-30.04</v>
+        <v>0.2616998637078467</v>
       </c>
       <c r="E5" t="n">
-        <v>902.4015999999999</v>
+        <v>0.06848681866470555</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>30.21</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>30.3981413549078</v>
       </c>
       <c r="D6" t="n">
-        <v>-30.21</v>
+        <v>0.1881413549078026</v>
       </c>
       <c r="E6" t="n">
-        <v>912.6441000000001</v>
+        <v>0.03539716942654374</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.22</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>30.79484862147722</v>
       </c>
       <c r="D7" t="n">
-        <v>-30.22</v>
+        <v>0.5748486214772228</v>
       </c>
       <c r="E7" t="n">
-        <v>913.2483999999999</v>
+        <v>0.3304509376142634</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.38</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>30.40182221066854</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.38</v>
+        <v>0.02182221066853884</v>
       </c>
       <c r="E8" t="n">
-        <v>922.9444</v>
+        <v>0.0004762088784620906</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.44</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>30.58925283100595</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.44</v>
+        <v>0.1492528310059456</v>
       </c>
       <c r="E9" t="n">
-        <v>926.5936</v>
+        <v>0.02227640756328934</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.48</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>30.76726524769149</v>
       </c>
       <c r="D10" t="n">
-        <v>-30.48</v>
+        <v>0.2872652476914901</v>
       </c>
       <c r="E10" t="n">
-        <v>929.0304</v>
+        <v>0.08252132253125315</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.69</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>30.65553389362031</v>
       </c>
       <c r="D11" t="n">
-        <v>-30.69</v>
+        <v>-0.03446610637968917</v>
       </c>
       <c r="E11" t="n">
-        <v>941.8761000000001</v>
+        <v>0.00118791248897605</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.75</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>30.46319840433761</v>
       </c>
       <c r="D12" t="n">
-        <v>-30.75</v>
+        <v>-0.2868015956623857</v>
       </c>
       <c r="E12" t="n">
-        <v>945.5625</v>
+        <v>0.08225515527449059</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.94</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>30.33826832813858</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.94</v>
+        <v>-0.6017316718614261</v>
       </c>
       <c r="E13" t="n">
-        <v>957.2836000000001</v>
+        <v>0.3620810049211469</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.95</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>30.91421946098578</v>
       </c>
       <c r="D14" t="n">
-        <v>-30.95</v>
+        <v>-0.03578053901421541</v>
       </c>
       <c r="E14" t="n">
-        <v>957.9024999999999</v>
+        <v>0.001280246972147791</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>31.02</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>31.08334631199928</v>
       </c>
       <c r="D15" t="n">
-        <v>-31.02</v>
+        <v>0.06334631199928253</v>
       </c>
       <c r="E15" t="n">
-        <v>962.2404</v>
+        <v>0.004012755243910446</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>31.12</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>31.37386341866624</v>
       </c>
       <c r="D16" t="n">
-        <v>-31.12</v>
+        <v>0.253863418666235</v>
       </c>
       <c r="E16" t="n">
-        <v>968.4544000000001</v>
+        <v>0.0644466353369081</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.28</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>31.35382061469859</v>
       </c>
       <c r="D17" t="n">
-        <v>-31.28</v>
+        <v>0.0738206146985867</v>
       </c>
       <c r="E17" t="n">
-        <v>978.4384000000001</v>
+        <v>0.005449483154477194</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.38</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>31.76592095163</v>
       </c>
       <c r="D18" t="n">
-        <v>-31.38</v>
+        <v>0.3859209516300055</v>
       </c>
       <c r="E18" t="n">
-        <v>984.7044</v>
+        <v>0.148934980907009</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.58</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>32.08039714711408</v>
       </c>
       <c r="D19" t="n">
-        <v>-31.58</v>
+        <v>0.5003971471140858</v>
       </c>
       <c r="E19" t="n">
-        <v>997.2963999999999</v>
+        <v>0.250397304839916</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.65</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>32.05691973869513</v>
       </c>
       <c r="D20" t="n">
-        <v>-31.65</v>
+        <v>0.4069197386951302</v>
       </c>
       <c r="E20" t="n">
-        <v>1001.7225</v>
+        <v>0.1655836737397131</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.88</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>31.72850874014626</v>
       </c>
       <c r="D21" t="n">
-        <v>-31.88</v>
+        <v>-0.1514912598537421</v>
       </c>
       <c r="E21" t="n">
-        <v>1016.3344</v>
+        <v>0.02294960181207402</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>32.28</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>32.34452537865486</v>
       </c>
       <c r="D22" t="n">
-        <v>-32.28</v>
+        <v>0.06452537865485652</v>
       </c>
       <c r="E22" t="n">
-        <v>1041.9984</v>
+        <v>0.004163524490552614</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>32.45</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>32.3279649760885</v>
       </c>
       <c r="D23" t="n">
-        <v>-32.45</v>
+        <v>-0.1220350239115078</v>
       </c>
       <c r="E23" t="n">
-        <v>1053.0025</v>
+        <v>0.01489254706108228</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.85</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>33.35621045423139</v>
       </c>
       <c r="D24" t="n">
-        <v>-32.85</v>
+        <v>0.5062104542313861</v>
       </c>
       <c r="E24" t="n">
-        <v>1079.1225</v>
+        <v>0.2562490239731463</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.9</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>33.01847596218533</v>
       </c>
       <c r="D25" t="n">
-        <v>-32.9</v>
+        <v>0.118475962185336</v>
       </c>
       <c r="E25" t="n">
-        <v>1082.41</v>
+        <v>0.01403655361574116</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>33.1</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>33.19891958886334</v>
       </c>
       <c r="D26" t="n">
-        <v>-33.1</v>
+        <v>0.09891958886333896</v>
       </c>
       <c r="E26" t="n">
-        <v>1095.61</v>
+        <v>0.009785085060892013</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>33.4</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>33.16046126621927</v>
       </c>
       <c r="D27" t="n">
-        <v>-33.4</v>
+        <v>-0.2395387337807335</v>
       </c>
       <c r="E27" t="n">
-        <v>1115.56</v>
+        <v>0.05737880498127713</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>33.7</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>33.7893257046001</v>
       </c>
       <c r="D28" t="n">
-        <v>-33.7</v>
+        <v>0.0893257046000997</v>
       </c>
       <c r="E28" t="n">
-        <v>1135.69</v>
+        <v>0.007979081502304272</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>34.1</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>34.5665080189096</v>
       </c>
       <c r="D29" t="n">
-        <v>-34.1</v>
+        <v>0.4665080189096003</v>
       </c>
       <c r="E29" t="n">
-        <v>1162.81</v>
+        <v>0.21762973170696</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>34.4</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>34.59969205759258</v>
       </c>
       <c r="D30" t="n">
-        <v>-34.4</v>
+        <v>0.1996920575925856</v>
       </c>
       <c r="E30" t="n">
-        <v>1183.36</v>
+        <v>0.03987691786556051</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>34.9</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>35.16502067223599</v>
       </c>
       <c r="D31" t="n">
-        <v>-34.9</v>
+        <v>0.2650206722359911</v>
       </c>
       <c r="E31" t="n">
-        <v>1218.01</v>
+        <v>0.07023595671241664</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>35.3</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>34.96264882611138</v>
       </c>
       <c r="D32" t="n">
-        <v>-35.3</v>
+        <v>-0.3373511738886137</v>
       </c>
       <c r="E32" t="n">
-        <v>1246.09</v>
+        <v>0.1138058145240257</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>35.7</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>35.26988327467259</v>
       </c>
       <c r="D33" t="n">
-        <v>-35.7</v>
+        <v>-0.4301167253274158</v>
       </c>
       <c r="E33" t="n">
-        <v>1274.49</v>
+        <v>0.1850003974063797</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>36.3</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>36.0186020077862</v>
       </c>
       <c r="D34" t="n">
-        <v>-36.3</v>
+        <v>-0.2813979922137975</v>
       </c>
       <c r="E34" t="n">
-        <v>1317.69</v>
+        <v>0.07918483002195642</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>36.8</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>36.39685792328989</v>
       </c>
       <c r="D35" t="n">
-        <v>-36.8</v>
+        <v>-0.4031420767101039</v>
       </c>
       <c r="E35" t="n">
-        <v>1354.24</v>
+        <v>0.1625235340141353</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>37.3</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>37.41331571183255</v>
       </c>
       <c r="D36" t="n">
-        <v>-37.3</v>
+        <v>0.1133157118325485</v>
       </c>
       <c r="E36" t="n">
-        <v>1391.29</v>
+        <v>0.01284045054811718</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>37.9</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>37.87972272349179</v>
       </c>
       <c r="D37" t="n">
-        <v>-37.9</v>
+        <v>-0.02027727650821021</v>
       </c>
       <c r="E37" t="n">
-        <v>1436.41</v>
+        <v>0.0004111679425904135</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>38.5</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>38.38858216854828</v>
       </c>
       <c r="D38" t="n">
-        <v>-38.5</v>
+        <v>-0.1114178314517247</v>
       </c>
       <c r="E38" t="n">
-        <v>1482.25</v>
+        <v>0.01241393316540493</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>38.9</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>39.22039050917978</v>
       </c>
       <c r="D39" t="n">
-        <v>-38.9</v>
+        <v>0.3203905091797807</v>
       </c>
       <c r="E39" t="n">
-        <v>1513.21</v>
+        <v>0.1026500783724792</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>39.4</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>39.91697248426966</v>
       </c>
       <c r="D40" t="n">
-        <v>-39.4</v>
+        <v>0.5169724842696581</v>
       </c>
       <c r="E40" t="n">
-        <v>1552.36</v>
+        <v>0.2672605494919419</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>39.9</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>40.06922978261161</v>
       </c>
       <c r="D41" t="n">
-        <v>-39.9</v>
+        <v>0.1692297826116089</v>
       </c>
       <c r="E41" t="n">
-        <v>1592.01</v>
+        <v>0.02863871932277241</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>40.1</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>39.85084667886793</v>
       </c>
       <c r="D42" t="n">
-        <v>-40.1</v>
+        <v>-0.24915332113207</v>
       </c>
       <c r="E42" t="n">
-        <v>1608.01</v>
+        <v>0.0620773774311404</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>40.6</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>41.03408562619104</v>
       </c>
       <c r="D43" t="n">
-        <v>-40.6</v>
+        <v>0.4340856261910346</v>
       </c>
       <c r="E43" t="n">
-        <v>1648.36</v>
+        <v>0.1884303308656627</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>40.9</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>41.26257785707261</v>
       </c>
       <c r="D44" t="n">
-        <v>-40.9</v>
+        <v>0.3625778570726084</v>
       </c>
       <c r="E44" t="n">
-        <v>1672.81</v>
+        <v>0.1314627024393648</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>41.2</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>41.01829683879443</v>
       </c>
       <c r="D45" t="n">
-        <v>-41.2</v>
+        <v>-0.1817031612055686</v>
       </c>
       <c r="E45" t="n">
-        <v>1697.44</v>
+        <v>0.03301603879209686</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>41.5</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>40.88273289387499</v>
       </c>
       <c r="D46" t="n">
-        <v>-41.5</v>
+        <v>-0.6172671061250057</v>
       </c>
       <c r="E46" t="n">
-        <v>1722.25</v>
+        <v>0.381018680303939</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>41.8</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>41.34702269434033</v>
       </c>
       <c r="D47" t="n">
-        <v>-41.8</v>
+        <v>-0.4529773056596653</v>
       </c>
       <c r="E47" t="n">
-        <v>1747.24</v>
+        <v>0.2051884394426899</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>42.2</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>41.86829395669196</v>
       </c>
       <c r="D48" t="n">
-        <v>-42.2</v>
+        <v>-0.3317060433080385</v>
       </c>
       <c r="E48" t="n">
-        <v>1780.84</v>
+        <v>0.1100288991670743</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>42.7</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>42.17851202908643</v>
       </c>
       <c r="D49" t="n">
-        <v>-42.7</v>
+        <v>-0.5214879709135758</v>
       </c>
       <c r="E49" t="n">
-        <v>1823.29</v>
+        <v>0.2719497038075585</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>43.7</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>43.42156435389256</v>
       </c>
       <c r="D50" t="n">
-        <v>-43.7</v>
+        <v>-0.2784356461074395</v>
       </c>
       <c r="E50" t="n">
-        <v>1909.69</v>
+        <v>0.07752640902326731</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>44.2</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>43.668173480221</v>
       </c>
       <c r="D51" t="n">
-        <v>-44.2</v>
+        <v>-0.5318265197790026</v>
       </c>
       <c r="E51" t="n">
-        <v>1953.64</v>
+        <v>0.2828394471402459</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1743.7</v>
+        <v>0.7732343401484449</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>61792.50440000001</v>
+        <v>5.111710176668966</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>1235.850088</v>
+        <v>0.1022342035333793</v>
       </c>
     </row>
   </sheetData>

--- a/full/sliding_window_results_window_9.xlsx
+++ b/full/sliding_window_results_window_9.xlsx
@@ -463,13 +463,13 @@
         <v>29.81</v>
       </c>
       <c r="C2" t="n">
-        <v>29.92086429301134</v>
+        <v>29.689789789984</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1108642930113426</v>
+        <v>-0.1202102100160012</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01229089146490483</v>
+        <v>0.01445049459209111</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.92</v>
       </c>
       <c r="C3" t="n">
-        <v>29.75576833558574</v>
+        <v>29.77464353928464</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1642316644142596</v>
+        <v>-0.1453564607153623</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02697203959627799</v>
+        <v>0.02112850067169668</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.98</v>
       </c>
       <c r="C4" t="n">
-        <v>30.13415867165269</v>
+        <v>29.95342292007426</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1541586716526879</v>
+        <v>-0.02657707992574032</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02376489604572125</v>
+        <v>0.0007063411773791891</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>30.04</v>
       </c>
       <c r="C5" t="n">
-        <v>30.30169986370785</v>
+        <v>30.08070802283664</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2616998637078467</v>
+        <v>0.04070802283663966</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06848681866470555</v>
+        <v>0.001657143123268376</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>30.21</v>
       </c>
       <c r="C6" t="n">
-        <v>30.3981413549078</v>
+        <v>29.9486969615396</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1881413549078026</v>
+        <v>-0.2613030384604045</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03539716942654374</v>
+        <v>0.06827927790863962</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.22</v>
       </c>
       <c r="C7" t="n">
-        <v>30.79484862147722</v>
+        <v>30.00784428344136</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5748486214772228</v>
+        <v>-0.212155716558641</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3304509376142634</v>
+        <v>0.0450100480685104</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.38</v>
       </c>
       <c r="C8" t="n">
-        <v>30.40182221066854</v>
+        <v>30.10529399001541</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02182221066853884</v>
+        <v>-0.2747060099845875</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0004762088784620906</v>
+        <v>0.07546339192165229</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.44</v>
       </c>
       <c r="C9" t="n">
-        <v>30.58925283100595</v>
+        <v>30.18106639863993</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1492528310059456</v>
+        <v>-0.2589336013600736</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02227640756328934</v>
+        <v>0.0670466099132975</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.48</v>
       </c>
       <c r="C10" t="n">
-        <v>30.76726524769149</v>
+        <v>30.41968846855577</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2872652476914901</v>
+        <v>-0.06031153144423129</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08252132253125315</v>
+        <v>0.0036374808251485</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.69</v>
       </c>
       <c r="C11" t="n">
-        <v>30.65553389362031</v>
+        <v>30.63199001373461</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.03446610637968917</v>
+        <v>-0.05800998626539311</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00118791248897605</v>
+        <v>0.003365158506511097</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.75</v>
       </c>
       <c r="C12" t="n">
-        <v>30.46319840433761</v>
+        <v>30.30284733939781</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2868015956623857</v>
+        <v>-0.4471526606021854</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08225515527449059</v>
+        <v>0.1999455018836132</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.94</v>
       </c>
       <c r="C13" t="n">
-        <v>30.33826832813858</v>
+        <v>30.63365575614692</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6017316718614261</v>
+        <v>-0.3063442438530792</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3620810049211469</v>
+        <v>0.09384679574191487</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.95</v>
       </c>
       <c r="C14" t="n">
-        <v>30.91421946098578</v>
+        <v>30.7508481746227</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.03578053901421541</v>
+        <v>-0.1991518253772959</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001280246972147791</v>
+        <v>0.03966144955110897</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>31.02</v>
       </c>
       <c r="C15" t="n">
-        <v>31.08334631199928</v>
+        <v>30.98109137593765</v>
       </c>
       <c r="D15" t="n">
-        <v>0.06334631199928253</v>
+        <v>-0.03890862406234774</v>
       </c>
       <c r="E15" t="n">
-        <v>0.004012755243910446</v>
+        <v>0.001513881026425106</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>31.12</v>
       </c>
       <c r="C16" t="n">
-        <v>31.37386341866624</v>
+        <v>31.13647901763622</v>
       </c>
       <c r="D16" t="n">
-        <v>0.253863418666235</v>
+        <v>0.01647901763621817</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0644466353369081</v>
+        <v>0.0002715580222547896</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.28</v>
       </c>
       <c r="C17" t="n">
-        <v>31.35382061469859</v>
+        <v>31.26541666893836</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0738206146985867</v>
+        <v>-0.01458333106163678</v>
       </c>
       <c r="E17" t="n">
-        <v>0.005449483154477194</v>
+        <v>0.0002126735448533003</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.38</v>
       </c>
       <c r="C18" t="n">
-        <v>31.76592095163</v>
+        <v>31.35457287112699</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3859209516300055</v>
+        <v>-0.0254271288730088</v>
       </c>
       <c r="E18" t="n">
-        <v>0.148934980907009</v>
+        <v>0.0006465388827245976</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.58</v>
       </c>
       <c r="C19" t="n">
-        <v>32.08039714711408</v>
+        <v>31.56061374389093</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5003971471140858</v>
+        <v>-0.01938625610906541</v>
       </c>
       <c r="E19" t="n">
-        <v>0.250397304839916</v>
+        <v>0.0003758269259262761</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.65</v>
       </c>
       <c r="C20" t="n">
-        <v>32.05691973869513</v>
+        <v>31.50105428730047</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4069197386951302</v>
+        <v>-0.1489457126995291</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1655836737397131</v>
+        <v>0.02218482533157065</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.88</v>
       </c>
       <c r="C21" t="n">
-        <v>31.72850874014626</v>
+        <v>31.74289705033951</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1514912598537421</v>
+        <v>-0.1371029496604912</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02294960181207402</v>
+        <v>0.01879721880560718</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>32.28</v>
       </c>
       <c r="C22" t="n">
-        <v>32.34452537865486</v>
+        <v>31.99087069477385</v>
       </c>
       <c r="D22" t="n">
-        <v>0.06452537865485652</v>
+        <v>-0.2891293052261474</v>
       </c>
       <c r="E22" t="n">
-        <v>0.004163524490552614</v>
+        <v>0.08359575514055473</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>32.45</v>
       </c>
       <c r="C23" t="n">
-        <v>32.3279649760885</v>
+        <v>32.1130876245282</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1220350239115078</v>
+        <v>-0.3369123754718046</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01489254706108228</v>
+        <v>0.1135099487460543</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.85</v>
       </c>
       <c r="C24" t="n">
-        <v>33.35621045423139</v>
+        <v>33.00262975347164</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5062104542313861</v>
+        <v>0.1526297534716363</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2562490239731463</v>
+        <v>0.02329584164481248</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.9</v>
       </c>
       <c r="C25" t="n">
-        <v>33.01847596218533</v>
+        <v>32.83643369402844</v>
       </c>
       <c r="D25" t="n">
-        <v>0.118475962185336</v>
+        <v>-0.06356630597156254</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01403655361574116</v>
+        <v>0.004040675254870308</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>33.1</v>
       </c>
       <c r="C26" t="n">
-        <v>33.19891958886334</v>
+        <v>32.95422166607396</v>
       </c>
       <c r="D26" t="n">
-        <v>0.09891958886333896</v>
+        <v>-0.1457783339260388</v>
       </c>
       <c r="E26" t="n">
-        <v>0.009785085060892013</v>
+        <v>0.02125132264225167</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>33.4</v>
       </c>
       <c r="C27" t="n">
-        <v>33.16046126621927</v>
+        <v>33.05385757930835</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2395387337807335</v>
+        <v>-0.346142420691649</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05737880498127713</v>
+        <v>0.1198145754022745</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>33.7</v>
       </c>
       <c r="C28" t="n">
-        <v>33.7893257046001</v>
+        <v>33.4866273020676</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0893257046000997</v>
+        <v>-0.2133726979323995</v>
       </c>
       <c r="E28" t="n">
-        <v>0.007979081502304272</v>
+        <v>0.04552790822295102</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>34.1</v>
       </c>
       <c r="C29" t="n">
-        <v>34.5665080189096</v>
+        <v>34.02113221464936</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4665080189096003</v>
+        <v>-0.07886778535063854</v>
       </c>
       <c r="E29" t="n">
-        <v>0.21762973170696</v>
+        <v>0.006220127566114396</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>34.4</v>
       </c>
       <c r="C30" t="n">
-        <v>34.59969205759258</v>
+        <v>34.20005211462632</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1996920575925856</v>
+        <v>-0.1999478853736747</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03987691786556051</v>
+        <v>0.03997915686540415</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>34.9</v>
       </c>
       <c r="C31" t="n">
-        <v>35.16502067223599</v>
+        <v>34.91611239506201</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2650206722359911</v>
+        <v>0.01611239506200945</v>
       </c>
       <c r="E31" t="n">
-        <v>0.07023595671241664</v>
+        <v>0.0002596092746342667</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>35.3</v>
       </c>
       <c r="C32" t="n">
-        <v>34.96264882611138</v>
+        <v>34.81910368792976</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3373511738886137</v>
+        <v>-0.4808963120702359</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1138058145240257</v>
+        <v>0.2312612629627537</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>35.7</v>
       </c>
       <c r="C33" t="n">
-        <v>35.26988327467259</v>
+        <v>35.35240472245677</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.4301167253274158</v>
+        <v>-0.3475952775432347</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1850003974063797</v>
+        <v>0.1208224769703584</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>36.3</v>
       </c>
       <c r="C34" t="n">
-        <v>36.0186020077862</v>
+        <v>36.10753236103567</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2813979922137975</v>
+        <v>-0.1924676389643238</v>
       </c>
       <c r="E34" t="n">
-        <v>0.07918483002195642</v>
+        <v>0.03704379204850131</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>36.8</v>
       </c>
       <c r="C35" t="n">
-        <v>36.39685792328989</v>
+        <v>36.63946727036621</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.4031420767101039</v>
+        <v>-0.1605327296337862</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1625235340141353</v>
+        <v>0.02577075728367429</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>37.3</v>
       </c>
       <c r="C36" t="n">
-        <v>37.41331571183255</v>
+        <v>37.30532086300951</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1133157118325485</v>
+        <v>0.00532086300951562</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01284045054811718</v>
+        <v>2.831158316603162e-05</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>37.9</v>
       </c>
       <c r="C37" t="n">
-        <v>37.87972272349179</v>
+        <v>37.93470255251436</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.02027727650821021</v>
+        <v>0.03470255251436072</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0004111679425904135</v>
+        <v>0.001204267151011963</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>38.5</v>
       </c>
       <c r="C38" t="n">
-        <v>38.38858216854828</v>
+        <v>38.25522591630553</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1114178314517247</v>
+        <v>-0.2447740836944732</v>
       </c>
       <c r="E38" t="n">
-        <v>0.01241393316540493</v>
+        <v>0.05991435204846896</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>38.9</v>
       </c>
       <c r="C39" t="n">
-        <v>39.22039050917978</v>
+        <v>38.74349198126436</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3203905091797807</v>
+        <v>-0.1565080187356429</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1026500783724792</v>
+        <v>0.02449475992855635</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>39.4</v>
       </c>
       <c r="C40" t="n">
-        <v>39.91697248426966</v>
+        <v>39.22100368337024</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5169724842696581</v>
+        <v>-0.1789963166297568</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2672605494919419</v>
+        <v>0.03203968136702015</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>39.9</v>
       </c>
       <c r="C41" t="n">
-        <v>40.06922978261161</v>
+        <v>39.4504346020169</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1692297826116089</v>
+        <v>-0.4495653979831005</v>
       </c>
       <c r="E41" t="n">
-        <v>0.02863871932277241</v>
+        <v>0.2021090470637035</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>40.1</v>
       </c>
       <c r="C42" t="n">
-        <v>39.85084667886793</v>
+        <v>40.1930017252669</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.24915332113207</v>
+        <v>0.09300172526689465</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0620773774311404</v>
+        <v>0.008649320902618952</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>40.6</v>
       </c>
       <c r="C43" t="n">
-        <v>41.03408562619104</v>
+        <v>40.43780829379854</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4340856261910346</v>
+        <v>-0.1621917062014617</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1884303308656627</v>
+        <v>0.02630614956054128</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>40.9</v>
       </c>
       <c r="C44" t="n">
-        <v>41.26257785707261</v>
+        <v>40.99265101225274</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3625778570726084</v>
+        <v>0.09265101225273753</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1314627024393648</v>
+        <v>0.00858421007145692</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>41.2</v>
       </c>
       <c r="C45" t="n">
-        <v>41.01829683879443</v>
+        <v>41.39418404459904</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1817031612055686</v>
+        <v>0.1941840445990337</v>
       </c>
       <c r="E45" t="n">
-        <v>0.03301603879209686</v>
+        <v>0.03770744317683952</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>41.5</v>
       </c>
       <c r="C46" t="n">
-        <v>40.88273289387499</v>
+        <v>41.17128416761626</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6172671061250057</v>
+        <v>-0.3287158323837431</v>
       </c>
       <c r="E46" t="n">
-        <v>0.381018680303939</v>
+        <v>0.1080540984597371</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>41.8</v>
       </c>
       <c r="C47" t="n">
-        <v>41.34702269434033</v>
+        <v>41.49119601891392</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4529773056596653</v>
+        <v>-0.3088039810860792</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2051884394426899</v>
+        <v>0.09535989873461156</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>42.2</v>
       </c>
       <c r="C48" t="n">
-        <v>41.86829395669196</v>
+        <v>41.94235509881112</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3317060433080385</v>
+        <v>-0.2576449011888826</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1100288991670743</v>
+        <v>0.06638089510862909</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>42.7</v>
       </c>
       <c r="C49" t="n">
-        <v>42.17851202908643</v>
+        <v>42.63286738736319</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5214879709135758</v>
+        <v>-0.06713261263681147</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2719497038075585</v>
+        <v>0.00450678767944418</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>43.7</v>
       </c>
       <c r="C50" t="n">
-        <v>43.42156435389256</v>
+        <v>43.63879797751901</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2784356461074395</v>
+        <v>-0.06120202248099105</v>
       </c>
       <c r="E50" t="n">
-        <v>0.07752640902326731</v>
+        <v>0.003745687555763733</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>44.2</v>
       </c>
       <c r="C51" t="n">
-        <v>43.668173480221</v>
+        <v>43.64220768487469</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5318265197790026</v>
+        <v>-0.5577923151253117</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2828394471402459</v>
+        <v>0.311132266812855</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.7732343401484449</v>
+        <v>-7.737313236681779</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>5.111710176668966</v>
+        <v>2.540811103653828</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.1022342035333793</v>
+        <v>0.05081622207307656</v>
       </c>
     </row>
   </sheetData>
